--- a/InputData/trans/BPP/Battery Pack Price.xlsx
+++ b/InputData/trans/BPP/Battery Pack Price.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\BPP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\BPP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48359E06-F382-4E1F-81F2-5E8970E7301D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5ECB2E4-46DF-4367-A783-5F31E1460F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>Sources:</t>
   </si>
@@ -43,15 +43,6 @@
     <t>BNEF</t>
   </si>
   <si>
-    <t>https://about.bnef.com/blog/lithium-ion-battery-pack-prices-rise-for-first-time-to-an-average-of-151-kwh/</t>
-  </si>
-  <si>
-    <t>Lithium-ion Battery Pack Prices Rise for First Time to an Average of $151/kWh</t>
-  </si>
-  <si>
-    <t>2012 to 2022 USD</t>
-  </si>
-  <si>
     <t>Price</t>
   </si>
   <si>
@@ -67,20 +58,20 @@
     <t>The EPS applies endogenous learning for battery pack prices in years where the battery pack price is listed as 0.</t>
   </si>
   <si>
-    <t>2022 to 2023</t>
-  </si>
-  <si>
     <t>Lithium-ion Battery Pack Prices Hit Record Low of $139/kWh</t>
   </si>
   <si>
     <t>https://about.bnef.com/blog/lithium-ion-battery-pack-prices-hit-record-low-of-139-kwh/#:~:text=Given%20this%2C%20BNEF%20expects%20average,and%20%2480%2FkWh%20in%202030.</t>
+  </si>
+  <si>
+    <t>2023 to 2012</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,6 +83,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -114,17 +113,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -141,9 +143,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -181,7 +183,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -287,7 +289,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -429,7 +431,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -437,15 +439,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF982137-6F01-4109-8226-D4C6F3731BA9}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
     <col min="2" max="2" width="101.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -458,67 +461,41 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>2</v>
+      <c r="B6" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>1</v>
+      <c r="A8" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="2">
-        <v>2023</v>
+      <c r="A9" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>1.29</v>
-      </c>
-      <c r="B16" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <f>1/0.951</f>
-        <v>1.0515247108307046</v>
-      </c>
-      <c r="B17" t="s">
-        <v>10</v>
+      <c r="B11" s="2">
+        <v>0.75350342301658668</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" location=":~:text=Given%20this%2C%20BNEF%20expects%20average,and%20%2480%2FkWh%20in%202030." xr:uid="{96C10B99-B75C-4A91-A1D1-2211BAD3764D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -533,7 +510,7 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -628,19 +605,19 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <f>141/About!$A$16</f>
-        <v>109.30232558139535</v>
+        <f>150*About!$B$11</f>
+        <v>113.025513452488</v>
       </c>
       <c r="C2">
-        <f>151/About!$A$16</f>
-        <v>117.05426356589147</v>
+        <f>161*About!$B$11</f>
+        <v>121.31405110567046</v>
       </c>
       <c r="D2">
-        <f>139/(About!A16*About!A17)</f>
-        <v>102.47209302325579</v>
+        <f>139*About!$B$11</f>
+        <v>104.73697579930555</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -739,7 +716,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B1">
         <v>2020</v>
@@ -747,11 +724,11 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <f>150/About!$A$16</f>
-        <v>116.27906976744185</v>
+        <f>160*About!B11</f>
+        <v>120.56054768265386</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/trans/BPP/Battery Pack Price.xlsx
+++ b/InputData/trans/BPP/Battery Pack Price.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\BPP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\BPP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5ECB2E4-46DF-4367-A783-5F31E1460F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{48359E06-F382-4E1F-81F2-5E8970E7301D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35093E7D-975F-44A6-9036-558B4E4F286B}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BPP" sheetId="2" r:id="rId2"/>
     <sheet name="SYBPP" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -35,7 +38,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+  <si>
+    <t>BPP Battery Pack Price</t>
+  </si>
   <si>
     <t>Sources:</t>
   </si>
@@ -43,35 +49,44 @@
     <t>BNEF</t>
   </si>
   <si>
+    <t>Lithium-Ion Battery Pack Prices See Largest Drop Since 2017, Falling to $115 per Kilowatt-Hour</t>
+  </si>
+  <si>
+    <t>https://about.bnef.com/blog/lithium-ion-battery-pack-prices-see-largest-drop-since-2017-falling-to-115-per-kilowatt-hour-bloombergnef/</t>
+  </si>
+  <si>
+    <t>Shruti M. Deorah, Nikit Abhyankar, Siddharth Arora, Ashwin Gambhir, Amol Phadke</t>
+  </si>
+  <si>
+    <t>Estimating the Cost of Grid-Scale Lithium-Ion Battery Storage in India</t>
+  </si>
+  <si>
+    <t>https://international.lbl.gov/publications/estimating-cost-grid-scale-lithium</t>
+  </si>
+  <si>
+    <t>Pg 27</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>The EPS applies endogenous learning for battery pack prices in years where the battery pack price is listed as 0.</t>
+  </si>
+  <si>
+    <t>Scaling ratio (India-U.S.)</t>
+  </si>
+  <si>
+    <t>$/kWh</t>
+  </si>
+  <si>
     <t>Price</t>
-  </si>
-  <si>
-    <t>$/kWh</t>
-  </si>
-  <si>
-    <t>BPP Battery Pack Price</t>
-  </si>
-  <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t>The EPS applies endogenous learning for battery pack prices in years where the battery pack price is listed as 0.</t>
-  </si>
-  <si>
-    <t>Lithium-ion Battery Pack Prices Hit Record Low of $139/kWh</t>
-  </si>
-  <si>
-    <t>https://about.bnef.com/blog/lithium-ion-battery-pack-prices-hit-record-low-of-139-kwh/#:~:text=Given%20this%2C%20BNEF%20expects%20average,and%20%2480%2FkWh%20in%202030.</t>
-  </si>
-  <si>
-    <t>2023 to 2012</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,13 +132,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -143,9 +161,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -183,7 +201,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -289,7 +307,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -431,7 +449,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -439,62 +457,89 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF982137-6F01-4109-8226-D4C6F3731BA9}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" customWidth="1"/>
     <col min="2" max="2" width="101.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="B5" s="2">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+    <row r="8" spans="1:2">
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="B9" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="B10" s="2">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="2">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+    <row r="12" spans="1:2">
+      <c r="B12" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="14" spans="1:2">
+      <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2">
-        <v>0.75350342301658668</v>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" location=":~:text=Given%20this%2C%20BNEF%20expects%20average,and%20%2480%2FkWh%20in%202030." xr:uid="{96C10B99-B75C-4A91-A1D1-2211BAD3764D}"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{3BF61351-841A-4131-B7D8-609DCF878EB2}"/>
+    <hyperlink ref="B11" r:id="rId2" xr:uid="{138CF80C-67B1-4442-959F-08A5A904B6E5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -506,11 +551,11 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -603,24 +648,25 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B2">
-        <f>150*About!$B$11</f>
-        <v>113.025513452488</v>
+        <f>155*About!A18</f>
+        <v>198.4</v>
       </c>
       <c r="C2">
-        <f>161*About!$B$11</f>
-        <v>121.31405110567046</v>
+        <f>166*About!A18</f>
+        <v>212.48000000000002</v>
       </c>
       <c r="D2">
-        <f>139*About!$B$11</f>
-        <v>104.73697579930555</v>
+        <f>144*About!A18</f>
+        <v>184.32</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <f>115*About!A18</f>
+        <v>147.20000000000002</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -712,26 +758,197 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B1">
         <v>2020</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B2">
-        <f>160*About!B11</f>
-        <v>120.56054768265386</v>
+        <f>165*About!A18</f>
+        <v>211.20000000000002</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2497F5F5-C3D7-4495-828B-505FCC751398}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{957AD26A-6CF0-414A-9295-36A62A73D644}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FFEB5B4-9CBB-419E-90A9-79C74374A9A7}"/>
 </file>